--- a/output/korea_semiconductor_equipment_market.xlsx
+++ b/output/korea_semiconductor_equipment_market.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="기관별_시장전망" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SEMI_실적" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="글로벌_참고" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="출처" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SEMI_국가별전망" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SEMI_실적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="글로벌_참고" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="출처" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);-"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);-"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0;(#,##0.0);-"/>
+    <numFmt numFmtId="167" formatCode="0%;(0%);-"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,8 +79,25 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00C55A11"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +117,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -168,6 +193,22 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1201,6 +1242,1266 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SEMI - 국가/지역별 반도체 장비 실적 및 전망 (단위: 십억달러, US$ B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>※ 중요 : SEMI는 국가별 '연도별' 전망을 2030년까지 공개하지 않습니다. 공개 범위 = 총장비 국가별은 실적(~2025)까지, 300mm 팹장비 국가별은 3년 누적(2026-2028)까지, 글로벌 연도별은 2029년(+성장률만 2031년)까지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>파란색 = SEMI 공식 발표 수치 / 주황색 = SEMI 공개 수치를 근거로 한 추정치(SEMI 공식 수치 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>① 총 반도체 장비 매출 실적 - 지역별 (SEMI + SEAJ, 2026.04 발표)  ※ 첨부하신 표와 동일 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>지역</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>YoY %</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2025 비중</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="D7" s="30">
+        <f>C7/B7-1</f>
+        <v/>
+      </c>
+      <c r="E7" s="30">
+        <f>C7/C$14</f>
+        <v/>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>성숙노드 중심, 사실상 보합. 2026년부터 완만한 감소 전망</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>대만</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D8" s="30">
+        <f>C8/B8-1</f>
+        <v/>
+      </c>
+      <c r="E8" s="30">
+        <f>C8/C$14</f>
+        <v/>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>TSMC 2nm 이하 첨단로직 증설, +90% 급증하며 2위</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="D9" s="33">
+        <f>C9/B9-1</f>
+        <v/>
+      </c>
+      <c r="E9" s="33">
+        <f>C9/C$14</f>
+        <v/>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>HBM·DRAM 투자 지속. 2024년 2위 → 2025년 3위</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>북미</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="D10" s="30">
+        <f>C10/B10-1</f>
+        <v/>
+      </c>
+      <c r="E10" s="30">
+        <f>C10/C$14</f>
+        <v/>
+      </c>
+      <c r="F10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="D11" s="30">
+        <f>C11/B11-1</f>
+        <v/>
+      </c>
+      <c r="E11" s="30">
+        <f>C11/C$14</f>
+        <v/>
+      </c>
+      <c r="F11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>유럽</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="D12" s="30">
+        <f>C12/B12-1</f>
+        <v/>
+      </c>
+      <c r="E12" s="30">
+        <f>C12/C$14</f>
+        <v/>
+      </c>
+      <c r="F12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="D13" s="30">
+        <f>C13/B13-1</f>
+        <v/>
+      </c>
+      <c r="E13" s="30">
+        <f>C13/C$14</f>
+        <v/>
+      </c>
+      <c r="F13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>전 세계 합계</t>
+        </is>
+      </c>
+      <c r="B14" s="35">
+        <f>SUM(B7:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="35">
+        <f>SUM(C7:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="30">
+        <f>C14/B14-1</f>
+        <v/>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>중국·대만·한국 합계가 전 세계의 79% (2024년 74%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>출처: SEMI, Worldwide Semiconductor Equipment Market Statistics (WWSEMS) / SEAJ, 2026.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/SEMI-Reports-Global-Semiconductor-Equipment-Billings-Reached-135-Billion-in-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>② 총 반도체 장비 - 글로벌 연도별 전망 (발표 시점별) ※ 국가별 금액은 미공개, 순위만 공개</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>발표시점</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>2027F</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>2028F</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>국가별 언급 내용</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>출처(URL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>25.12 연말전망</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="n">
+        <v>133</v>
+      </c>
+      <c r="C21" s="29" t="n">
+        <v>145</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <v>156</v>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>중국·대만·한국이 2027년까지 상위 3대 시장 유지 (금액 미공개). 한국은 첨단 메모리(HBM) 투자가 견인</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/semi-press-release/global-semiconductor-equipment-sales-projected-to-reach-a-record-of-156-billion-dollars-in-2027-semi-reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>26.04 실적확정</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="n">
+        <v>135.1</v>
+      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>2025년 실적 확정. 중국 49.3 / 대만 31.5 / 한국 25.8</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/SEMI-Reports-Global-Semiconductor-Equipment-Billings-Reached-135-Billion-in-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>26.07 연중전망(OEM)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="29" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="29" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>중국·대만·한국이 2028년까지 상위 3대 시장 유지 (금액 미공개). 한국은 첨단 메모리(HBM)가 견인</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/semi-press-release/global-semiconductor-equipment-sales-forecast-to-reach-a-record-229-billion-dollars-in-2028-semi-reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>③ 300mm 팹장비(Fab Equipment) - 글로벌 연도별 전망  ※ SEMI가 국가 단위로 가장 멀리 보는 데이터셋</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>2027F</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2028F</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>2029F</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>2030F</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>2031F</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>글로벌 300mm 팹장비 투자</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="C28" s="29" t="n">
+        <v>133</v>
+      </c>
+      <c r="D28" s="29" t="n">
+        <v>151</v>
+      </c>
+      <c r="E28" s="29" t="n">
+        <v>155</v>
+      </c>
+      <c r="F28" s="29" t="n">
+        <v>172</v>
+      </c>
+      <c r="G28" s="36">
+        <f>F28*(1-0.03)</f>
+        <v/>
+      </c>
+      <c r="H28" s="36">
+        <f>G28*(1+0.01)</f>
+        <v/>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>2026·2027은 26.04 발표, 2028·2029는 300mm Fab Outlook. 2030(-3%)·2031(+1%)은 SEMI가 성장률만 공개 → 금액은 역산 추정</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>YoY %</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="30">
+        <f>C28/B28-1</f>
+        <v/>
+      </c>
+      <c r="D29" s="30">
+        <f>D28/C28-1</f>
+        <v/>
+      </c>
+      <c r="E29" s="30">
+        <f>E28/D28-1</f>
+        <v/>
+      </c>
+      <c r="F29" s="30">
+        <f>F28/E28-1</f>
+        <v/>
+      </c>
+      <c r="G29" s="30">
+        <f>G28/F28-1</f>
+        <v/>
+      </c>
+      <c r="H29" s="30">
+        <f>H28/G28-1</f>
+        <v/>
+      </c>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>출처: SEMI 300mm Fab Outlook (2026.04) / SEMI 300mm Fab Outlook 제품 페이지(2029~2031 확장 전망)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/semi-press-release/semi-projects-double-digit-growth-in-global-300mm-fab-equipment-spending-for-2026-and-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/products-services/market-data/300mm-fab-outlook</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>④ 300mm 팹장비 - 국가/지역별 3년 누적 투자액  ※ SEMI가 공개하는 유일한 '국가별 전망' 형태</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>국가/지역</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>2025-2027 누적 (24.10 발표)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>2026-2028 누적 (25.10 발표)</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>비중</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>연평균 환산</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="B37" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="C37" s="29" t="n">
+        <v>94</v>
+      </c>
+      <c r="D37" s="30">
+        <f>IF(C37="","",C37/SUM(C$37:C$43))</f>
+        <v/>
+      </c>
+      <c r="E37" s="37">
+        <f>C37/3</f>
+        <v/>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>자급률 정책. 2024년 450억달러 정점 → 2027년 310억달러로 점진 감소 전망</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="B38" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="C38" s="32" t="n">
+        <v>86</v>
+      </c>
+      <c r="D38" s="33">
+        <f>IF(C38="","",C38/SUM(C$37:C$43))</f>
+        <v/>
+      </c>
+      <c r="E38" s="38">
+        <f>C38/3</f>
+        <v/>
+      </c>
+      <c r="F38" s="34" t="inlineStr">
+        <is>
+          <t>DRAM·HBM·3D NAND. 2위 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>대만</t>
+        </is>
+      </c>
+      <c r="B39" s="29" t="n">
+        <v>75</v>
+      </c>
+      <c r="C39" s="29" t="n">
+        <v>75</v>
+      </c>
+      <c r="D39" s="30">
+        <f>IF(C39="","",C39/SUM(C$37:C$43))</f>
+        <v/>
+      </c>
+      <c r="E39" s="37">
+        <f>C39/3</f>
+        <v/>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>3nm 이하 첨단로직이 주 동인</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>미주(Americas)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="29" t="n">
+        <v>60</v>
+      </c>
+      <c r="D40" s="30">
+        <f>IF(C40="","",C40/SUM(C$37:C$43))</f>
+        <v/>
+      </c>
+      <c r="E40" s="37">
+        <f>C40/3</f>
+        <v/>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>칩스법 기반 현지화. 2024년 120억 → 2027년 247억달러로 2배 확대 전망</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="B41" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="C41" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="D41" s="30">
+        <f>IF(C41="","",C41/SUM(C$37:C$43))</f>
+        <v/>
+      </c>
+      <c r="E41" s="37">
+        <f>C41/3</f>
+        <v/>
+      </c>
+      <c r="F41" s="21" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>유럽·중동</t>
+        </is>
+      </c>
+      <c r="B42" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="C42" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="D42" s="30">
+        <f>IF(C42="","",C42/SUM(C$37:C$43))</f>
+        <v/>
+      </c>
+      <c r="E42" s="37">
+        <f>C42/3</f>
+        <v/>
+      </c>
+      <c r="F42" s="21" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>동남아</t>
+        </is>
+      </c>
+      <c r="B43" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="C43" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="D43" s="30">
+        <f>IF(C43="","",C43/SUM(C$37:C$43))</f>
+        <v/>
+      </c>
+      <c r="E43" s="37">
+        <f>C43/3</f>
+        <v/>
+      </c>
+      <c r="F43" s="21" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B44" s="37">
+        <f>SUM(B37:B43)</f>
+        <v/>
+      </c>
+      <c r="C44" s="37">
+        <f>SUM(C37:C43)</f>
+        <v/>
+      </c>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>24.10 발표분 합계 약 4,000억달러 / 25.10 발표분 합계 3,740억달러</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>출처: SEMI '300mm Fab Equipment Spending $374B Over Next Three Years'(25.10) / 'Invest $400 Billion in 300mm Fab Equipment'(24.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/semi-press-release/semi-reports-global-300mm-fab-equipment-spending-expected-to-total-374-billion-dollars-over-next-three-years</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="28" t="inlineStr">
+        <is>
+          <t>⑤ 300mm 팹장비 - 국가별 연도별 수치 (SEMI 보도자료에 개별 언급된 것만, 발표 시점 상이하므로 시계열 혼용 주의)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>국가/지역</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>2027F</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>발표시점</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="B51" s="39" t="n"/>
+      <c r="C51" s="32" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D51" s="32" t="n">
+        <v>27</v>
+      </c>
+      <c r="E51" s="32" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="F51" s="40" t="inlineStr">
+        <is>
+          <t>25.10 / 24.10</t>
+        </is>
+      </c>
+      <c r="G51" s="34" t="inlineStr">
+        <is>
+          <t>2025 +29%, 2026 +26%. 2027 수치는 24.10 발표분</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>대만</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="29" t="n">
+        <v>21</v>
+      </c>
+      <c r="D52" s="29" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E52" s="29" t="n">
+        <v>28</v>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>25.10 / 24.10</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="B53" s="29" t="n">
+        <v>45</v>
+      </c>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="29" t="n">
+        <v>31</v>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>24.10</t>
+        </is>
+      </c>
+      <c r="G53" s="21" t="inlineStr">
+        <is>
+          <t>2024년 450억달러 정점 후 점진 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>미주</t>
+        </is>
+      </c>
+      <c r="B54" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="C54" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="D54" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="E54" s="29" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>25.10 / 24.10</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="inlineStr">
+        <is>
+          <t>3년간 2배 이상 확대</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="D55" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="E55" s="29" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>25.10 / 24.10</t>
+        </is>
+      </c>
+      <c r="G55" s="21" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>유럽·중동</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="29" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>24.10</t>
+        </is>
+      </c>
+      <c r="G56" s="21" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>동남아</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>24.10</t>
+        </is>
+      </c>
+      <c r="G57" s="21" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>※ 빈칸은 SEMI가 해당 연도 금액을 공개하지 않은 것. 서로 다른 발표 시점의 수치가 섞여 있어 같은 행이라도 연속된 시계열이 아님.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
+          <t>⑥ [추정] 2029~2030년 국가별 300mm 팹장비 투자  ※ SEMI 공식 수치 아님. 아래 가정에 따른 계산값</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>가정 : ③의 글로벌 연도별 전망(2029년 1,720억, 2030년 -3%)에 ④의 2026-2028 누적 국가별 비중이 그대로 유지된다고 가정하여 배분</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>국가/지역</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>비중 (2026-28 누적 기준)</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>2029F 추정</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>2030F 추정</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="B64" s="30">
+        <f>C37/C$44</f>
+        <v/>
+      </c>
+      <c r="C64" s="36">
+        <f>$B64*F$28</f>
+        <v/>
+      </c>
+      <c r="D64" s="36">
+        <f>$B64*G$28</f>
+        <v/>
+      </c>
+      <c r="E64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="B65" s="30">
+        <f>C38/C$44</f>
+        <v/>
+      </c>
+      <c r="C65" s="36">
+        <f>$B65*F$28</f>
+        <v/>
+      </c>
+      <c r="D65" s="36">
+        <f>$B65*G$28</f>
+        <v/>
+      </c>
+      <c r="E65" s="21" t="inlineStr">
+        <is>
+          <t>비중 23% 유지 가정 시 2030년 약 380억달러 수준</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="inlineStr">
+        <is>
+          <t>대만</t>
+        </is>
+      </c>
+      <c r="B66" s="30">
+        <f>C39/C$44</f>
+        <v/>
+      </c>
+      <c r="C66" s="36">
+        <f>$B66*F$28</f>
+        <v/>
+      </c>
+      <c r="D66" s="36">
+        <f>$B66*G$28</f>
+        <v/>
+      </c>
+      <c r="E66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>미주(Americas)</t>
+        </is>
+      </c>
+      <c r="B67" s="30">
+        <f>C40/C$44</f>
+        <v/>
+      </c>
+      <c r="C67" s="36">
+        <f>$B67*F$28</f>
+        <v/>
+      </c>
+      <c r="D67" s="36">
+        <f>$B67*G$28</f>
+        <v/>
+      </c>
+      <c r="E67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="19" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="B68" s="30">
+        <f>C41/C$44</f>
+        <v/>
+      </c>
+      <c r="C68" s="36">
+        <f>$B68*F$28</f>
+        <v/>
+      </c>
+      <c r="D68" s="36">
+        <f>$B68*G$28</f>
+        <v/>
+      </c>
+      <c r="E68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>유럽·중동</t>
+        </is>
+      </c>
+      <c r="B69" s="30">
+        <f>C42/C$44</f>
+        <v/>
+      </c>
+      <c r="C69" s="36">
+        <f>$B69*F$28</f>
+        <v/>
+      </c>
+      <c r="D69" s="36">
+        <f>$B69*G$28</f>
+        <v/>
+      </c>
+      <c r="E69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="19" t="inlineStr">
+        <is>
+          <t>동남아</t>
+        </is>
+      </c>
+      <c r="B70" s="30">
+        <f>C43/C$44</f>
+        <v/>
+      </c>
+      <c r="C70" s="36">
+        <f>$B70*F$28</f>
+        <v/>
+      </c>
+      <c r="D70" s="36">
+        <f>$B70*G$28</f>
+        <v/>
+      </c>
+      <c r="E70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B71" s="30">
+        <f>SUM(B64:B70)</f>
+        <v/>
+      </c>
+      <c r="C71" s="37">
+        <f>SUM(C64:C70)</f>
+        <v/>
+      </c>
+      <c r="D71" s="37">
+        <f>SUM(D64:D70)</f>
+        <v/>
+      </c>
+      <c r="E71" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>[추정의 한계]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>· SEMI는 2029년 이후 국가별 배분을 공개하지 않으며, 실제로는 중국 비중 감소·미주 비중 증가가 전망되고 있어 비중 고정 가정은 보수적입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>· 300mm 팹장비는 총 반도체 장비(①②)보다 좁은 범위입니다(200mm·테스트·후공정 장비 제외). 총장비 기준으로는 2025년 한국이 300mm 215억 vs 총장비 258억으로 약 1.2배 차이.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>· 2030년까지 국가별 연도별 공식 수치가 반드시 필요하시면 SEMI World Fab Forecast / 300mm Fab Outlook 유료 구독(분기 갱신)이 유일한 경로입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>SEMI World Fab Forecast: https://www.semi.org/en/products-services/market-data/world-fab-forecast</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId7"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1648,7 +2949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2048,7 +3349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/korea_semiconductor_equipment_market.xlsx
+++ b/output/korea_semiconductor_equipment_market.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.0;(#,##0.0);-"/>
     <numFmt numFmtId="167" formatCode="0%;(0%);-"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,6 +96,18 @@
       <color rgb="00C55A11"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -151,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -209,6 +221,10 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1242,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2029,454 +2045,644 @@
     <row r="49">
       <c r="A49" s="28" t="inlineStr">
         <is>
-          <t>⑤ 300mm 팹장비 - 국가별 연도별 수치 (SEMI 보도자료에 개별 언급된 것만, 발표 시점 상이하므로 시계열 혼용 주의)</t>
+          <t>⑤ 300mm 팹장비 - 국가별 연도별 수치  ※ 발표 자료(vintage)별로 구분. 자료가 다르면 시계열로 이어붙일 수 없음</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>국가/지역</t>
+          <t>발표 자료 / 국가</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>2026F</t>
-        </is>
-      </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>2027F</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>발표시점</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>비고</t>
+          <t>출처 URL</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="B51" s="39" t="n"/>
-      <c r="C51" s="32" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="D51" s="32" t="n">
-        <v>27</v>
-      </c>
-      <c r="E51" s="32" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="F51" s="40" t="inlineStr">
-        <is>
-          <t>25.10 / 24.10</t>
-        </is>
-      </c>
-      <c r="G51" s="34" t="inlineStr">
-        <is>
-          <t>2025 +29%, 2026 +26%. 2027 수치는 24.10 발표분</t>
-        </is>
-      </c>
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>[A] SEMI '300mm Fab Outlook to 2027' - 2024.03.19 발표  ※ 2027년 국가별 합계 136.9 = 발표 총액 137과 일치(검산 완료)</t>
+        </is>
+      </c>
+      <c r="B51" s="42" t="n"/>
+      <c r="C51" s="42" t="n"/>
+      <c r="D51" s="42" t="n"/>
+      <c r="E51" s="42" t="n"/>
+      <c r="F51" s="42" t="n"/>
+      <c r="G51" s="42" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>대만</t>
+          <t xml:space="preserve">    글로벌 300mm 합계</t>
         </is>
       </c>
       <c r="B52" s="5" t="n"/>
-      <c r="C52" s="29" t="n">
-        <v>21</v>
-      </c>
+      <c r="C52" s="5" t="n"/>
       <c r="D52" s="29" t="n">
-        <v>24.5</v>
+        <v>116.5</v>
       </c>
       <c r="E52" s="29" t="n">
-        <v>28</v>
-      </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>25.10 / 24.10</t>
-        </is>
-      </c>
-      <c r="G52" s="21" t="inlineStr"/>
+        <v>130.5</v>
+      </c>
+      <c r="F52" s="29" t="n">
+        <v>137</v>
+      </c>
+      <c r="G52" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/news-media-press-releases/semi-press-releases/300mm-fab-equipment-spending-forecast-to-reach-record-$137-billion-in-2027-semi-reports</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
         <is>
-          <t>중국</t>
-        </is>
-      </c>
-      <c r="B53" s="29" t="n">
-        <v>45</v>
-      </c>
+          <t xml:space="preserve">    중국</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n"/>
       <c r="C53" s="5" t="n"/>
       <c r="D53" s="5" t="n"/>
-      <c r="E53" s="29" t="n">
-        <v>31</v>
-      </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>24.10</t>
-        </is>
-      </c>
-      <c r="G53" s="21" t="inlineStr">
-        <is>
-          <t>2024년 450억달러 정점 후 점진 감소</t>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="G53" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/news-media-press-releases/semi-press-releases/300mm-fab-equipment-spending-forecast-to-reach-record-$137-billion-in-2027-semi-reports</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>미주</t>
-        </is>
-      </c>
-      <c r="B54" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="C54" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="D54" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="E54" s="29" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>25.10 / 24.10</t>
-        </is>
-      </c>
-      <c r="G54" s="21" t="inlineStr">
-        <is>
-          <t>3년간 2배 이상 확대</t>
+          <t xml:space="preserve">    대만</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="29" t="n">
+        <v>28</v>
+      </c>
+      <c r="G54" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/news-media-press-releases/semi-press-releases/300mm-fab-equipment-spending-forecast-to-reach-record-$137-billion-in-2027-semi-reports</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>일본</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="D55" s="29" t="n">
-        <v>11</v>
-      </c>
-      <c r="E55" s="29" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>25.10 / 24.10</t>
-        </is>
-      </c>
-      <c r="G55" s="21" t="inlineStr"/>
+      <c r="A55" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    한국</t>
+        </is>
+      </c>
+      <c r="B55" s="39" t="n"/>
+      <c r="C55" s="39" t="n"/>
+      <c r="D55" s="39" t="n"/>
+      <c r="E55" s="39" t="n"/>
+      <c r="F55" s="32" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G55" s="43" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/news-media-press-releases/semi-press-releases/300mm-fab-equipment-spending-forecast-to-reach-record-$137-billion-in-2027-semi-reports</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>유럽·중동</t>
+          <t xml:space="preserve">    미주(Americas)</t>
         </is>
       </c>
       <c r="B56" s="5" t="n"/>
-      <c r="C56" s="5" t="n"/>
+      <c r="C56" s="29" t="n">
+        <v>12</v>
+      </c>
       <c r="D56" s="5" t="n"/>
-      <c r="E56" s="29" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>24.10</t>
-        </is>
-      </c>
-      <c r="G56" s="21" t="inlineStr"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="29" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G56" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/news-media-press-releases/semi-press-releases/300mm-fab-equipment-spending-forecast-to-reach-record-$137-billion-in-2027-semi-reports</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="19" t="inlineStr">
         <is>
-          <t>동남아</t>
+          <t xml:space="preserve">    일본</t>
         </is>
       </c>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="5" t="n"/>
       <c r="D57" s="5" t="n"/>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="29" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G57" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/news-media-press-releases/semi-press-releases/300mm-fab-equipment-spending-forecast-to-reach-record-$137-billion-in-2027-semi-reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    유럽·중동</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="29" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G58" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/news-media-press-releases/semi-press-releases/300mm-fab-equipment-spending-forecast-to-reach-record-$137-billion-in-2027-semi-reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    동남아</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="29" t="n">
         <v>5.3</v>
       </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>24.10</t>
-        </is>
-      </c>
-      <c r="G57" s="21" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>※ 빈칸은 SEMI가 해당 연도 금액을 공개하지 않은 것. 서로 다른 발표 시점의 수치가 섞여 있어 같은 행이라도 연속된 시계열이 아님.</t>
-        </is>
-      </c>
+      <c r="G59" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/news-media-press-releases/semi-press-releases/300mm-fab-equipment-spending-forecast-to-reach-record-$137-billion-in-2027-semi-reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="41" t="inlineStr">
+        <is>
+          <t>[B] SEMI '$400B in 300mm Fab Equipment (2025-2027)' - 2024.10 발표 (SCMP 인용)</t>
+        </is>
+      </c>
+      <c r="B60" s="42" t="n"/>
+      <c r="C60" s="42" t="n"/>
+      <c r="D60" s="42" t="n"/>
+      <c r="E60" s="42" t="n"/>
+      <c r="F60" s="42" t="n"/>
+      <c r="G60" s="42" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="28" t="inlineStr">
-        <is>
-          <t>⑥ [추정] 2029~2030년 국가별 300mm 팹장비 투자  ※ SEMI 공식 수치 아님. 아래 가정에 따른 계산값</t>
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    중국</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="29" t="n">
+        <v>45</v>
+      </c>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="29" t="n">
+        <v>31</v>
+      </c>
+      <c r="G61" s="22" t="inlineStr">
+        <is>
+          <t>https://www.scmp.com/tech/tech-trends/article/3280146/china-south-korea-taiwan-spend-most-chip-equipment-2025-2027-industry-body-says</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>가정 : ③의 글로벌 연도별 전망(2029년 1,720억, 2030년 -3%)에 ④의 2026-2028 누적 국가별 비중이 그대로 유지된다고 가정하여 배분</t>
-        </is>
-      </c>
+      <c r="A62" s="41" t="inlineStr">
+        <is>
+          <t>[C] SEMI '300mm Fab Outlook to 2026' - 2023.07 발표  ※ 구(舊) vintage, 현재 전망과 크게 상이하므로 추세 참고용</t>
+        </is>
+      </c>
+      <c r="B62" s="42" t="n"/>
+      <c r="C62" s="42" t="n"/>
+      <c r="D62" s="42" t="n"/>
+      <c r="E62" s="42" t="n"/>
+      <c r="F62" s="42" t="n"/>
+      <c r="G62" s="42" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>국가/지역</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>비중 (2026-28 누적 기준)</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>2029F 추정</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>2030F 추정</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    글로벌 300mm 합계</t>
+        </is>
+      </c>
+      <c r="B63" s="29" t="n">
+        <v>74</v>
+      </c>
+      <c r="C63" s="29" t="n">
+        <v>82</v>
+      </c>
+      <c r="D63" s="29" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="E63" s="29" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/news-media-press-releases/semi-press-releases/global-300mm-fab-equipment-spending-forecast-to-reach-record-$119-billion-in-2026-semi-reports</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="19" t="inlineStr">
-        <is>
-          <t>중국</t>
-        </is>
-      </c>
-      <c r="B64" s="30">
-        <f>C37/C$44</f>
-        <v/>
-      </c>
-      <c r="C64" s="36">
-        <f>$B64*F$28</f>
-        <v/>
-      </c>
-      <c r="D64" s="36">
-        <f>$B64*G$28</f>
-        <v/>
-      </c>
-      <c r="E64" s="5" t="n"/>
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    한국</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="C64" s="39" t="n"/>
+      <c r="D64" s="39" t="n"/>
+      <c r="E64" s="32" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="F64" s="39" t="n"/>
+      <c r="G64" s="43" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/news-media-press-releases/semi-press-releases/global-300mm-fab-equipment-spending-forecast-to-reach-record-$119-billion-in-2026-semi-reports</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="B65" s="30">
-        <f>C38/C$44</f>
-        <v/>
-      </c>
-      <c r="C65" s="36">
-        <f>$B65*F$28</f>
-        <v/>
-      </c>
-      <c r="D65" s="36">
-        <f>$B65*G$28</f>
-        <v/>
-      </c>
-      <c r="E65" s="21" t="inlineStr">
-        <is>
-          <t>비중 23% 유지 가정 시 2030년 약 380억달러 수준</t>
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    대만</t>
+        </is>
+      </c>
+      <c r="B65" s="29" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="29" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/news-media-press-releases/semi-press-releases/global-300mm-fab-equipment-spending-forecast-to-reach-record-$119-billion-in-2026-semi-reports</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="19" t="inlineStr">
         <is>
-          <t>대만</t>
-        </is>
-      </c>
-      <c r="B66" s="30">
-        <f>C39/C$44</f>
-        <v/>
-      </c>
-      <c r="C66" s="36">
-        <f>$B66*F$28</f>
-        <v/>
-      </c>
-      <c r="D66" s="36">
-        <f>$B66*G$28</f>
-        <v/>
-      </c>
-      <c r="E66" s="5" t="n"/>
+          <t xml:space="preserve">    중국</t>
+        </is>
+      </c>
+      <c r="B66" s="29" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="29" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/news-media-press-releases/semi-press-releases/global-300mm-fab-equipment-spending-forecast-to-reach-record-$119-billion-in-2026-semi-reports</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">    미주(Americas)</t>
+        </is>
+      </c>
+      <c r="B67" s="29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="29" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="22" t="inlineStr">
+        <is>
+          <t>https://www.semi.org/en/news-media-press-releases/semi-press-releases/global-300mm-fab-equipment-spending-forecast-to-reach-record-$119-billion-in-2026-semi-reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="44" t="inlineStr">
+        <is>
+          <t>[D] 출처 확인 실패로 표에서 제외한 수치</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>· 한국 2025년 21.5 / 2026년 27.0, 대만 21.0 / 24.5, 미주 14.0 / 20.0, 일본 14.0 / 11.0 (십억달러)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → 웹 검색 요약에는 나타났으나 이를 담은 SEMI 보도자료를 특정하지 못했고, ④의 3년 누적치와도 합이 맞지 않아 제외했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (검산: 한국 21.5+27.0+26.3=74.8 vs SEMI 발표 2025-27 누적 81 / 일본 14.0+11.0+11.4=36.4 vs 발표 누적 32 → 불일치)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>· 중국 2027년 값은 자료별로 30(2024.03 발표)과 31(2024.10 발표)로 다릅니다. 두 값 모두 병기했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>⑥ [추정] 2029~2030년 국가별 300mm 팹장비 투자  ※ SEMI 공식 수치 아님. 아래 가정에 따른 계산값</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>가정 : ③의 글로벌 연도별 전망(2029년 1,720억, 2030년 -3%)에 ④의 2026-2028 누적 국가별 비중이 그대로 유지된다고 가정하여 배분</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>국가/지역</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>비중 (2026-28 누적 기준)</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>2029F 추정</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>2030F 추정</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="19" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="B80" s="30">
+        <f>C37/C$44</f>
+        <v/>
+      </c>
+      <c r="C80" s="36">
+        <f>$B80*F$28</f>
+        <v/>
+      </c>
+      <c r="D80" s="36">
+        <f>$B80*G$28</f>
+        <v/>
+      </c>
+      <c r="E80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="B81" s="30">
+        <f>C38/C$44</f>
+        <v/>
+      </c>
+      <c r="C81" s="36">
+        <f>$B81*F$28</f>
+        <v/>
+      </c>
+      <c r="D81" s="36">
+        <f>$B81*G$28</f>
+        <v/>
+      </c>
+      <c r="E81" s="21" t="inlineStr">
+        <is>
+          <t>비중 23% 유지 가정 시 2030년 약 380억달러 수준</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="19" t="inlineStr">
+        <is>
+          <t>대만</t>
+        </is>
+      </c>
+      <c r="B82" s="30">
+        <f>C39/C$44</f>
+        <v/>
+      </c>
+      <c r="C82" s="36">
+        <f>$B82*F$28</f>
+        <v/>
+      </c>
+      <c r="D82" s="36">
+        <f>$B82*G$28</f>
+        <v/>
+      </c>
+      <c r="E82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
           <t>미주(Americas)</t>
         </is>
       </c>
-      <c r="B67" s="30">
+      <c r="B83" s="30">
         <f>C40/C$44</f>
         <v/>
       </c>
-      <c r="C67" s="36">
-        <f>$B67*F$28</f>
-        <v/>
-      </c>
-      <c r="D67" s="36">
-        <f>$B67*G$28</f>
-        <v/>
-      </c>
-      <c r="E67" s="5" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="19" t="inlineStr">
+      <c r="C83" s="36">
+        <f>$B83*F$28</f>
+        <v/>
+      </c>
+      <c r="D83" s="36">
+        <f>$B83*G$28</f>
+        <v/>
+      </c>
+      <c r="E83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="19" t="inlineStr">
         <is>
           <t>일본</t>
         </is>
       </c>
-      <c r="B68" s="30">
+      <c r="B84" s="30">
         <f>C41/C$44</f>
         <v/>
       </c>
-      <c r="C68" s="36">
-        <f>$B68*F$28</f>
-        <v/>
-      </c>
-      <c r="D68" s="36">
-        <f>$B68*G$28</f>
-        <v/>
-      </c>
-      <c r="E68" s="5" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="19" t="inlineStr">
+      <c r="C84" s="36">
+        <f>$B84*F$28</f>
+        <v/>
+      </c>
+      <c r="D84" s="36">
+        <f>$B84*G$28</f>
+        <v/>
+      </c>
+      <c r="E84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="19" t="inlineStr">
         <is>
           <t>유럽·중동</t>
         </is>
       </c>
-      <c r="B69" s="30">
+      <c r="B85" s="30">
         <f>C42/C$44</f>
         <v/>
       </c>
-      <c r="C69" s="36">
-        <f>$B69*F$28</f>
-        <v/>
-      </c>
-      <c r="D69" s="36">
-        <f>$B69*G$28</f>
-        <v/>
-      </c>
-      <c r="E69" s="5" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="19" t="inlineStr">
+      <c r="C85" s="36">
+        <f>$B85*F$28</f>
+        <v/>
+      </c>
+      <c r="D85" s="36">
+        <f>$B85*G$28</f>
+        <v/>
+      </c>
+      <c r="E85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="19" t="inlineStr">
         <is>
           <t>동남아</t>
         </is>
       </c>
-      <c r="B70" s="30">
+      <c r="B86" s="30">
         <f>C43/C$44</f>
         <v/>
       </c>
-      <c r="C70" s="36">
-        <f>$B70*F$28</f>
-        <v/>
-      </c>
-      <c r="D70" s="36">
-        <f>$B70*G$28</f>
-        <v/>
-      </c>
-      <c r="E70" s="5" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="C86" s="36">
+        <f>$B86*F$28</f>
+        <v/>
+      </c>
+      <c r="D86" s="36">
+        <f>$B86*G$28</f>
+        <v/>
+      </c>
+      <c r="E86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B71" s="30">
-        <f>SUM(B64:B70)</f>
-        <v/>
-      </c>
-      <c r="C71" s="37">
-        <f>SUM(C64:C70)</f>
-        <v/>
-      </c>
-      <c r="D71" s="37">
-        <f>SUM(D64:D70)</f>
-        <v/>
-      </c>
-      <c r="E71" s="5" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="17" t="inlineStr">
+      <c r="B87" s="30">
+        <f>SUM(B80:B86)</f>
+        <v/>
+      </c>
+      <c r="C87" s="37">
+        <f>SUM(C80:C86)</f>
+        <v/>
+      </c>
+      <c r="D87" s="37">
+        <f>SUM(D80:D86)</f>
+        <v/>
+      </c>
+      <c r="E87" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
         <is>
           <t>[추정의 한계]</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>· SEMI는 2029년 이후 국가별 배분을 공개하지 않으며, 실제로는 중국 비중 감소·미주 비중 증가가 전망되고 있어 비중 고정 가정은 보수적입니다.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>· 300mm 팹장비는 총 반도체 장비(①②)보다 좁은 범위입니다(200mm·테스트·후공정 장비 제외). 총장비 기준으로는 2025년 한국이 300mm 215억 vs 총장비 258억으로 약 1.2배 차이.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>· 2030년까지 국가별 연도별 공식 수치가 반드시 필요하시면 SEMI World Fab Forecast / 300mm Fab Outlook 유료 구독(분기 갱신)이 유일한 경로입니다.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="16" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
         <is>
           <t>SEMI World Fab Forecast: https://www.semi.org/en/products-services/market-data/world-fab-forecast</t>
         </is>
@@ -2491,6 +2697,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/korea_semiconductor_equipment_market.xlsx
+++ b/output/korea_semiconductor_equipment_market.xlsx
@@ -959,7 +959,7 @@
       </c>
       <c r="R8" s="10" t="inlineStr">
         <is>
-          <t>원문 페이지 표기는 'USD Million'이나 세그먼트 수치 정합상 Billion 오기로 판단해 백만달러로 환산. 발표 CAGR과 앵커값 불일치</t>
+          <t>★단위 주의 : 원문 페이지는 총액·세그먼트 모두 'USD Million'으로 표기(2024년 9.63 Million). 그러나 SEMI 한국 장비 실적(2024년 205억달러) 및 타 기관 대비 1,000배 차이라 Billion 오기로 판단하고 백만달러(9,630)로 환산해 표기함 — 환산은 당사 판단이며 MRFR 원문 표기가 아님. 또한 발표 CAGR 7.779%와 자사 앵커값 내재 CAGR 8.59%가 불일치.</t>
         </is>
       </c>
       <c r="S8" s="11" t="inlineStr">
@@ -1163,6 +1163,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
